--- a/skills/ga-tintas-automation/output/precos_suvinil.xlsx
+++ b/skills/ga-tintas-automation/output/precos_suvinil.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Fontes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo de Preços'!$A$4:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo de Preços'!$A$4:$J$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -332,12 +332,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Comparativo'!$A$4:$A$15</f>
+              <f>'Comparativo'!$A$4:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Comparativo'!$C$4:$C$15</f>
+              <f>'Comparativo'!$C$4:$C$18</f>
             </numRef>
           </val>
         </ser>
@@ -356,12 +356,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Comparativo'!$A$4:$A$15</f>
+              <f>'Comparativo'!$A$4:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Comparativo'!$D$4:$D$15</f>
+              <f>'Comparativo'!$D$4:$D$18</f>
             </numRef>
           </val>
         </ser>
@@ -437,7 +437,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="10080000" cy="5760000"/>
@@ -747,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -772,7 +772,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pesquisa de mercado | Gerado em: 20/03/2026 18:46</t>
+          <t>Pesquisa de mercado | Gerado em: 20/03/2026 19:26</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>3.6L</t>
+          <t>18L</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>até 60 m²/demão</t>
+          <t>até 300 m²/demão</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1056,11 +1056,11 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Casa Costa Tintas</t>
+          <t>Obramax</t>
         </is>
       </c>
       <c r="I9" s="5" t="n">
-        <v>89.90000000000001</v>
+        <v>299.9</v>
       </c>
       <c r="J9" s="4" t="n"/>
     </row>
@@ -1102,107 +1102,105 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
+          <t>Casa Costa Tintas</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="J10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Suvinil Rende &amp; Cobre Muito Fosco</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Standard</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>até 60 m²/demão</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>Telhanorte</t>
         </is>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="I11" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="J10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Suvinil Fosco Completo</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Tinta Acrílica Premium</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="J11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Suvinil Rende &amp; Cobre Muito Fosco</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Standard</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Fosco</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>18L</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>até 380 m²/demão</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>até 60 m²/demão</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Interno e Externo</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Mercado Livre</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>358.8</v>
-      </c>
-      <c r="J11" s="7" t="n">
-        <v>478.4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Suvinil Fosco Completo</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Tinta Acrílica Premium</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Fosco</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>18L</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>até 380 m²/demão</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Interno e Externo</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Telhanorte</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>419.9</v>
-      </c>
-      <c r="J12" s="6" t="n"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="J12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1242,13 +1240,15 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Arena Tintas</t>
+          <t>Mercado Livre</t>
         </is>
       </c>
       <c r="I13" s="7" t="n">
-        <v>399</v>
-      </c>
-      <c r="J13" s="6" t="n"/>
+        <v>358.8</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>478.4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>3.6L</t>
+          <t>18L</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>até 76 m²/demão</t>
+          <t>até 380 m²/demão</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="I14" s="7" t="n">
-        <v>109.9</v>
+        <v>419.9</v>
       </c>
       <c r="J14" s="6" t="n"/>
     </row>
@@ -1319,330 +1319,328 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>até 380 m²/demão</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Arena Tintas</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>399</v>
+      </c>
+      <c r="J15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Suvinil Fosco Completo</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Premium</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>até 380 m²/demão</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>389.9</v>
+      </c>
+      <c r="J16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Suvinil Fosco Completo</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Premium</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
           <t>3.6L</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>até 76 m²/demão</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Interno e Externo</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Telhanorte</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="J17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Suvinil Fosco Completo</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Premium</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>até 76 m²/demão</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>Bela Tintas</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="I18" s="7" t="n">
         <v>115</v>
       </c>
-      <c r="J15" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="J18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Select</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Suvinil Toque Fosco Select</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Tinta Acrílica Alto Padrão</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Fosco Aveludado</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>até 350 m²/demão</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>Interno</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>Mercado Livre</t>
         </is>
       </c>
-      <c r="I16" s="9" t="n">
+      <c r="I19" s="9" t="n">
         <v>759.73</v>
       </c>
-      <c r="J16" s="9" t="n">
+      <c r="J19" s="9" t="n">
         <v>799.72</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Select</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Suvinil Toque Fosco Select</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Tinta Acrílica Alto Padrão</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Fosco Aveludado</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>até 350 m²/demão</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>Interno</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Mercado Livre (2)</t>
         </is>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I20" s="9" t="n">
         <v>414.76</v>
       </c>
-      <c r="J17" s="9" t="n">
+      <c r="J20" s="9" t="n">
         <v>524.9400000000001</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Select</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Suvinil Toque Fosco Select</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Tinta Acrílica Alto Padrão</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Fosco Aveludado</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>até 350 m²/demão</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>Interno</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Arena Tintas</t>
         </is>
       </c>
-      <c r="I18" s="9" t="n">
+      <c r="I21" s="9" t="n">
         <v>689</v>
       </c>
-      <c r="J18" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Esmaltes</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>Suvinil Esmalte Cor &amp; Proteção Base Água Acetinado</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Esmalte Base Água</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Acetinado</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>3.6L</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>até 60 m²/demão</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Interno e Externo (metal e madeira)</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>Arena Tintas</t>
-        </is>
-      </c>
-      <c r="I19" s="11" t="n">
-        <v>265.16</v>
-      </c>
-      <c r="J19" s="11" t="n">
-        <v>294.62</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Esmaltes</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Suvinil Esmalte Cor &amp; Proteção Base Água Acetinado</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Esmalte Base Água</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Acetinado</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>3.6L</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>até 60 m²/demão</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>Interno e Externo (metal e madeira)</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>Leroy Merlin</t>
-        </is>
-      </c>
-      <c r="I20" s="11" t="n">
-        <v>289.9</v>
-      </c>
-      <c r="J20" s="10" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>Esmaltes</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>Suvinil Esmalte Cor &amp; Proteção Grafite Fosco</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Esmalte Anticorrosivo</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Grafite Fosco</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>3.6L</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>até 50 m²/demão</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>Metal (aplica direto na ferrugem)</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>Arena Tintas</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="n">
-        <v>308.09</v>
-      </c>
-      <c r="J21" s="10" t="n"/>
+      <c r="J21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Especiais</t>
+          <t>Esmaltes</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Suvinil Epóxi</t>
+          <t>Suvinil Esmalte Cor &amp; Proteção Base Água Acetinado</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Tinta Epóxi</t>
+          <t>Esmalte Base Água</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Brilhante</t>
+          <t>Acetinado</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
@@ -1652,12 +1650,12 @@
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>até 45 m²/demão</t>
+          <t>até 60 m²/demão</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Garagens, áreas industriais, cozinhas</t>
+          <t>Interno e Externo (metal e madeira)</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
@@ -1666,334 +1664,658 @@
         </is>
       </c>
       <c r="I22" s="11" t="n">
-        <v>327.97</v>
-      </c>
-      <c r="J22" s="10" t="n"/>
+        <v>265.16</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>294.62</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
+          <t>Esmaltes</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Suvinil Esmalte Cor &amp; Proteção Base Água Acetinado</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Esmalte Base Água</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Acetinado</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>até 60 m²/demão</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>Interno e Externo (metal e madeira)</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>Leroy Merlin</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>289.9</v>
+      </c>
+      <c r="J23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Esmaltes</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Suvinil Esmalte Cor &amp; Proteção Grafite Fosco</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Esmalte Anticorrosivo</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Grafite Fosco</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>até 50 m²/demão</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Metal (aplica direto na ferrugem)</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Arena Tintas</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>308.09</v>
+      </c>
+      <c r="J24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
           <t>Especiais</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>Suvinil Epóxi</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>Tinta Epóxi</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>Brilhante</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>3.6L</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>até 45 m²/demão</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Garagens, áreas industriais, cozinhas</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>Arena Tintas</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="n">
+        <v>327.97</v>
+      </c>
+      <c r="J25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Especiais</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Suvinil Epóxi</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Tinta Epóxi</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Brilhante</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>até 45 m²/demão</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Garagens, áreas industriais, cozinhas</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>Leroy Merlin</t>
         </is>
       </c>
-      <c r="I23" s="11" t="n">
+      <c r="I26" s="11" t="n">
         <v>349.9</v>
       </c>
-      <c r="J23" s="10" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="J26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Econômica</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Suvinil Látex Maxx</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>Tinta Látex Econômica</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>Fosco</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>até 280 m²/demão</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>Interno</t>
         </is>
       </c>
-      <c r="H24" s="12" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>Bela Tintas</t>
         </is>
       </c>
-      <c r="I24" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>189.9</v>
       </c>
-      <c r="J24" s="12" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="J27" s="12" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Econômica</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Suvinil Látex Maxx</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>Tinta Látex Econômica</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>Fosco</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>até 280 m²/demão</t>
         </is>
       </c>
-      <c r="G25" s="12" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>Interno</t>
         </is>
       </c>
-      <c r="H25" s="12" t="inlineStr">
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>Mercado Livre</t>
         </is>
       </c>
-      <c r="I25" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>169.9</v>
       </c>
-      <c r="J25" s="12" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="J28" s="12" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Econômica</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Suvinil Látex Maxx</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>Tinta Látex Econômica</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>Fosco</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>3.6L</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>até 56 m²/demão</t>
         </is>
       </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>Interno</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr">
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>Bela Tintas</t>
         </is>
       </c>
-      <c r="I26" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>49.9</v>
       </c>
-      <c r="J26" s="12" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="J29" s="12" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Pisos</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Suvinil Piso Acrílica</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Tinta Acrílica para Pisos</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>Fosco</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>até 250 m²/demão</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>Pisos de concreto, cimento, cerâmicos</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>Leroy Merlin</t>
         </is>
       </c>
-      <c r="I27" s="5" t="n">
+      <c r="I30" s="5" t="n">
         <v>339.9</v>
       </c>
-      <c r="J27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="J30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Pisos</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Suvinil Piso Acrílica</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica para Pisos</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>até 250 m²/demão</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Pisos de concreto, cimento, cerâmicos</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="J31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Suvinil Rende &amp; Cobre Muito Fosco (Obramax 20L)</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Standard</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>até 189 m² acabado</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="J32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo (Obramax 20L)</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Premium</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>até 167 m² acabado</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>449.9</v>
+      </c>
+      <c r="J33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Econômica</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>Suvinil Glasu Econômica (Obramax 20L)</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Econômica</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>até 200 m²/demão</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="J34" s="12" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Suvinil Inova Fosco Sempre Limpo</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>Tinta Acrílica Premium Anti-Mancha</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>Fosco</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>até 350 m²/demão</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>Interno e Externo (lavável)</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>Arena Tintas</t>
         </is>
       </c>
-      <c r="I28" s="7" t="n">
+      <c r="I35" s="7" t="n">
         <v>499</v>
       </c>
-      <c r="J28" s="6" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="J35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Suvinil Inova Fosco Sempre Limpo</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>Tinta Acrílica Premium Anti-Mancha</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>Fosco</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>até 350 m²/demão</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>Interno e Externo (lavável)</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr">
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>Leroy Merlin</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n">
+      <c r="I36" s="7" t="n">
         <v>529.9</v>
       </c>
-      <c r="J29" s="6" t="n"/>
+      <c r="J36" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J29"/>
+  <autoFilter ref="A4:J36"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -2008,7 +2330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2082,7 +2404,7 @@
         <v>339.07</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>287.5625</v>
+        <v>290.03</v>
       </c>
       <c r="F4" s="16" t="n">
         <v>0.6358066383635661</v>
@@ -2105,20 +2427,20 @@
         </is>
       </c>
       <c r="C5" s="15" t="n">
-        <v>89.90000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>95</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>92.45</v>
+        <v>88.26666666666667</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>0.05672969966629582</v>
+        <v>0.1889862327909886</v>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>Casa Costa Tintas</t>
+          <t>Obramax</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2462,7 @@
         <v>419.9</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>392.5666666666667</v>
+        <v>391.9</v>
       </c>
       <c r="F6" s="19" t="n">
         <v>0.1702898550724637</v>
@@ -2366,47 +2688,134 @@
         </is>
       </c>
       <c r="C14" s="15" t="n">
-        <v>339.9</v>
+        <v>329.9</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>339.9</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>339.9</v>
+        <v>334.9</v>
       </c>
       <c r="F14" s="16" t="n">
+        <v>0.03031221582297666</v>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Suvinil Rende &amp; Cobre Muito Fosco (Obramax 20L)</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="F15" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>Leroy Merlin</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo (Obramax 20L)</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>449.9</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>449.9</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>449.9</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>Suvinil Glasu Econômica (Obramax 20L)</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="D17" s="27" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="F17" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="26" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Suvinil Inova Fosco Sempre Limpo</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C18" s="18" t="n">
         <v>499</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D18" s="18" t="n">
         <v>529.9</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E18" s="18" t="n">
         <v>514.45</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F18" s="19" t="n">
         <v>0.06192384769539074</v>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>Arena Tintas</t>
         </is>
@@ -2427,7 +2836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2496,7 +2905,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>287.5625</v>
+        <v>290.03</v>
       </c>
       <c r="D5" s="30">
         <f>C5*0.75</f>
@@ -2523,7 +2932,7 @@
         </is>
       </c>
       <c r="C6" s="30" t="n">
-        <v>92.45</v>
+        <v>88.26666666666667</v>
       </c>
       <c r="D6" s="30">
         <f>C6*0.75</f>
@@ -2550,7 +2959,7 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>392.5666666666667</v>
+        <v>391.9</v>
       </c>
       <c r="D7" s="33">
         <f>C7*0.75</f>
@@ -2766,7 +3175,7 @@
         </is>
       </c>
       <c r="C15" s="30" t="n">
-        <v>339.9</v>
+        <v>334.9</v>
       </c>
       <c r="D15" s="30">
         <f>C15*0.75</f>
@@ -2782,41 +3191,122 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>Suvinil Rende &amp; Cobre Muito Fosco (Obramax 20L)</t>
+        </is>
+      </c>
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="C16" s="30" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="D16" s="30">
+        <f>C16*0.75</f>
+        <v/>
+      </c>
+      <c r="E16" s="30">
+        <f>C16*0.60</f>
+        <v/>
+      </c>
+      <c r="F16" s="31">
+        <f>(D16-E16)/D16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo (Obramax 20L)</t>
+        </is>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="C17" s="33" t="n">
+        <v>449.9</v>
+      </c>
+      <c r="D17" s="33">
+        <f>C17*0.75</f>
+        <v/>
+      </c>
+      <c r="E17" s="33">
+        <f>C17*0.60</f>
+        <v/>
+      </c>
+      <c r="F17" s="34">
+        <f>(D17-E17)/D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="41" t="inlineStr">
+        <is>
+          <t>Suvinil Glasu Econômica (Obramax 20L)</t>
+        </is>
+      </c>
+      <c r="B18" s="41" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="C18" s="42" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="D18" s="42">
+        <f>C18*0.75</f>
+        <v/>
+      </c>
+      <c r="E18" s="42">
+        <f>C18*0.60</f>
+        <v/>
+      </c>
+      <c r="F18" s="43">
+        <f>(D18-E18)/D18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>Suvinil Inova Fosco Sempre Limpo</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="C16" s="33" t="n">
+      <c r="C19" s="33" t="n">
         <v>514.45</v>
       </c>
-      <c r="D16" s="33">
-        <f>C16*0.75</f>
-        <v/>
-      </c>
-      <c r="E16" s="33">
-        <f>C16*0.60</f>
-        <v/>
-      </c>
-      <c r="F16" s="34">
-        <f>(D16-E16)/D16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="44" t="inlineStr">
+      <c r="D19" s="33">
+        <f>C19*0.75</f>
+        <v/>
+      </c>
+      <c r="E19" s="33">
+        <f>C19*0.60</f>
+        <v/>
+      </c>
+      <c r="F19" s="34">
+        <f>(D19-E19)/D19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="44" t="inlineStr">
         <is>
           <t>AVISO: Os preços estimados de distribuidor e fábrica são aproximações baseadas em margens típicas do setor.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="44" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="44" t="inlineStr">
         <is>
           <t>Margens reais variam conforme volume, negociação e política comercial de cada fabricante.</t>
         </is>
@@ -2837,7 +3327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3039,6 +3529,74 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="47" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+      <c r="B14" s="47" t="inlineStr">
+        <is>
+          <t>https://www.obramax.com.br/suvinil</t>
+        </is>
+      </c>
+      <c r="C14" s="47" t="inlineStr">
+        <is>
+          <t>Home center atacado/varejo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="47" t="inlineStr">
+        <is>
+          <t>Cofema Atacadista</t>
+        </is>
+      </c>
+      <c r="B15" s="47" t="inlineStr">
+        <is>
+          <t>https://www.cofema.com.br/</t>
+        </is>
+      </c>
+      <c r="C15" s="47" t="inlineStr">
+        <is>
+          <t>Atacadista materiais construção</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="47" t="inlineStr">
+        <is>
+          <t>Eletroleste</t>
+        </is>
+      </c>
+      <c r="B16" s="47" t="inlineStr">
+        <is>
+          <t>https://www.eletroleste.com.br/</t>
+        </is>
+      </c>
+      <c r="C16" s="47" t="inlineStr">
+        <is>
+          <t>Atacadista materiais construção</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="47" t="inlineStr">
+        <is>
+          <t>Smarfer</t>
+        </is>
+      </c>
+      <c r="B17" s="47" t="inlineStr">
+        <is>
+          <t>N/D (fonte do cliente)</t>
+        </is>
+      </c>
+      <c r="C17" s="47" t="inlineStr">
+        <is>
+          <t>Distribuidora (a confirmar)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/skills/ga-tintas-automation/output/precos_suvinil.xlsx
+++ b/skills/ga-tintas-automation/output/precos_suvinil.xlsx
@@ -772,7 +772,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pesquisa de mercado | Gerado em: 20/03/2026 19:26</t>
+          <t>Pesquisa de mercado | Gerado em: 20/03/2026 20:00</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
     <row r="17">
       <c r="A17" s="47" t="inlineStr">
         <is>
-          <t>Smarfer</t>
+          <t>Ismafer</t>
         </is>
       </c>
       <c r="B17" s="47" t="inlineStr">
         <is>
-          <t>N/D (fonte do cliente)</t>
+          <t>https://www.ismafer.com.br/</t>
         </is>
       </c>
       <c r="C17" s="47" t="inlineStr">
         <is>
-          <t>Distribuidora (a confirmar)</t>
+          <t>Varejo ferragens e ferramentas</t>
         </is>
       </c>
     </row>

--- a/skills/ga-tintas-automation/output/precos_suvinil.xlsx
+++ b/skills/ga-tintas-automation/output/precos_suvinil.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Fontes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo de Preços'!$A$4:$J$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo de Preços'!$A$4:$J$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -113,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -152,6 +152,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -199,6 +205,15 @@
     <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -214,10 +229,12 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -332,12 +349,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Comparativo'!$A$4:$A$18</f>
+              <f>'Comparativo'!$A$4:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Comparativo'!$C$4:$C$18</f>
+              <f>'Comparativo'!$C$4:$C$25</f>
             </numRef>
           </val>
         </ser>
@@ -356,12 +373,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Comparativo'!$A$4:$A$18</f>
+              <f>'Comparativo'!$A$4:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Comparativo'!$D$4:$D$18</f>
+              <f>'Comparativo'!$D$4:$D$25</f>
             </numRef>
           </val>
         </ser>
@@ -437,7 +454,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="10080000" cy="5760000"/>
@@ -747,7 +764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -772,7 +789,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pesquisa de mercado | Gerado em: 20/03/2026 20:00</t>
+          <t>Pesquisa de mercado | Gerado em: 20/03/2026 20:38</t>
         </is>
       </c>
     </row>
@@ -851,12 +868,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>18L</t>
+          <t>0.9L</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>até 300 m²/demão</t>
+          <t>até 25 m² acabado</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -866,15 +883,13 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Mercado Livre</t>
+          <t>Construtintas</t>
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>339.07</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>423.84</v>
-      </c>
+        <v>39.9</v>
+      </c>
+      <c r="J5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -899,12 +914,12 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>18L</t>
+          <t>0.9L</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>até 300 m²/demão</t>
+          <t>até 25 m² acabado</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -914,15 +929,13 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Varejão das Tintas</t>
+          <t>Hipertintas</t>
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>319</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>354.44</v>
-      </c>
+        <v>39.9</v>
+      </c>
+      <c r="J6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -947,12 +960,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>18L</t>
+          <t>0.9L</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>até 300 m²/demão</t>
+          <t>até 25 m² acabado</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -962,11 +975,11 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>São Geraldo Tintas</t>
+          <t>Arena Tintas</t>
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>284.9</v>
+        <v>35.3</v>
       </c>
       <c r="J7" s="4" t="n"/>
     </row>
@@ -993,12 +1006,12 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>18L</t>
+          <t>0.9L</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>até 300 m²/demão</t>
+          <t>até 25 m² acabado</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -1008,15 +1021,13 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Mercado Livre (2)</t>
+          <t>Magazine Luiza</t>
         </is>
       </c>
       <c r="I8" s="5" t="n">
-        <v>207.28</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>323.89</v>
-      </c>
+        <v>38.9</v>
+      </c>
+      <c r="J8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1041,12 +1052,12 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>18L</t>
+          <t>3.6L</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>até 300 m²/demão</t>
+          <t>até 100 m²/demão</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1056,11 +1067,11 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Obramax</t>
+          <t>Hipertintas</t>
         </is>
       </c>
       <c r="I9" s="5" t="n">
-        <v>299.9</v>
+        <v>115.9</v>
       </c>
       <c r="J9" s="4" t="n"/>
     </row>
@@ -1092,7 +1103,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>até 60 m²/demão</t>
+          <t>até 100 m²/demão</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1102,11 +1113,11 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Casa Costa Tintas</t>
+          <t>Rei das Tintas</t>
         </is>
       </c>
       <c r="I10" s="5" t="n">
-        <v>89.90000000000001</v>
+        <v>128</v>
       </c>
       <c r="J10" s="4" t="n"/>
     </row>
@@ -1138,7 +1149,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>até 60 m²/demão</t>
+          <t>até 100 m²/demão</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1148,11 +1159,11 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Telhanorte</t>
+          <t>Casa Costa Tintas</t>
         </is>
       </c>
       <c r="I11" s="5" t="n">
-        <v>95</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="J11" s="4" t="n"/>
     </row>
@@ -1184,7 +1195,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>até 60 m²/demão</t>
+          <t>até 100 m²/demão</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1194,941 +1205,941 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
+          <t>Telhanorte</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="J12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Suvinil Rende &amp; Cobre Muito Fosco</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Standard</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>até 100 m²/demão</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
           <t>Obramax</t>
         </is>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="I13" s="5" t="n">
         <v>79.90000000000001</v>
       </c>
-      <c r="J12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="J13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Suvinil Rende &amp; Cobre Muito Fosco</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Standard</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>até 300 m²/demão</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Mercado Livre</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>339.07</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>423.84</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Suvinil Rende &amp; Cobre Muito Fosco</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Standard</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>até 300 m²/demão</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Varejão das Tintas</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>319</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>354.44</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Suvinil Rende &amp; Cobre Muito Fosco</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Standard</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>até 300 m²/demão</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>São Geraldo Tintas</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>284.9</v>
+      </c>
+      <c r="J16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Suvinil Rende &amp; Cobre Muito Fosco</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Standard</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>até 300 m²/demão</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Mercado Livre (2)</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>207.28</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>323.89</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Suvinil Rende &amp; Cobre Muito Fosco</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Standard</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>até 300 m²/demão</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="J18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Suvinil Rende &amp; Cobre Muito Fosco</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Standard</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>até 189 m² acabado</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="J19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Suvinil Rende &amp; Cobre Muito Fosco</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Standard</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>até 189 m² acabado</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Mercado Livre</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>391.69</v>
+      </c>
+      <c r="J20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Suvinil Tetos Acrílica Fosca</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Standard para Tetos</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>até 23 m² acabado</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Interno e Externo coberto</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="J21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Suvinil Tetos Acrílica Fosca</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Standard para Tetos</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>até 23 m² acabado</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Interno e Externo coberto</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Telhanorte</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="J22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Suvinil Fosco Completo</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Tinta Acrílica Premium</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Fosco</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>0.9L</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>até 15 m² acabado</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Hipertintas</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="J23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Premium</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>até 30 m² acabado</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Hipertintas</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>139.9</v>
+      </c>
+      <c r="J24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Premium</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>até 30 m² acabado</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Hipertintas (Areia)</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>185.9</v>
+      </c>
+      <c r="J25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Premium</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>até 30 m² acabado</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Telhanorte</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="J26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Premium</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>até 30 m² acabado</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Bela Tintas</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>115</v>
+      </c>
+      <c r="J27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Premium</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>até 30 m² acabado</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Interno e Externo</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="J28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Premium</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>até 380 m²/demão</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>Interno e Externo</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>Mercado Livre</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I29" s="7" t="n">
         <v>358.8</v>
       </c>
-      <c r="J13" s="7" t="n">
+      <c r="J29" s="7" t="n">
         <v>478.4</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Suvinil Fosco Completo</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Tinta Acrílica Premium</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>Fosco</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>até 380 m²/demão</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>Interno e Externo</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>Telhanorte</t>
         </is>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I30" s="7" t="n">
         <v>419.9</v>
       </c>
-      <c r="J14" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="J30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Suvinil Fosco Completo</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Tinta Acrílica Premium</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>Fosco</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>até 380 m²/demão</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>Interno e Externo</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>Arena Tintas</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="I31" s="7" t="n">
         <v>399</v>
       </c>
-      <c r="J15" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="J31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Suvinil Fosco Completo</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Tinta Acrílica Premium</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>Fosco</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>até 380 m²/demão</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>Interno e Externo</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>Obramax</t>
         </is>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="I32" s="7" t="n">
         <v>389.9</v>
       </c>
-      <c r="J16" s="6" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Suvinil Fosco Completo</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Tinta Acrílica Premium</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Fosco</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>3.6L</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>até 76 m²/demão</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Interno e Externo</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Telhanorte</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>109.9</v>
-      </c>
-      <c r="J17" s="6" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Suvinil Fosco Completo</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Tinta Acrílica Premium</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Fosco</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>3.6L</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>até 76 m²/demão</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>Interno e Externo</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Bela Tintas</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>115</v>
-      </c>
-      <c r="J18" s="6" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Select</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Suvinil Toque Fosco Select</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Tinta Acrílica Alto Padrão</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Fosco Aveludado</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>18L</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>até 350 m²/demão</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>Interno</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>Mercado Livre</t>
-        </is>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>759.73</v>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>799.72</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>Select</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Suvinil Toque Fosco Select</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Tinta Acrílica Alto Padrão</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Fosco Aveludado</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>18L</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>até 350 m²/demão</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>Interno</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>Mercado Livre (2)</t>
-        </is>
-      </c>
-      <c r="I20" s="9" t="n">
-        <v>414.76</v>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>524.9400000000001</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Select</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Suvinil Toque Fosco Select</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Tinta Acrílica Alto Padrão</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Fosco Aveludado</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>18L</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>até 350 m²/demão</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>Interno</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>Arena Tintas</t>
-        </is>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>689</v>
-      </c>
-      <c r="J21" s="8" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Esmaltes</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>Suvinil Esmalte Cor &amp; Proteção Base Água Acetinado</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>Esmalte Base Água</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Acetinado</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>3.6L</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>até 60 m²/demão</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>Interno e Externo (metal e madeira)</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>Arena Tintas</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="n">
-        <v>265.16</v>
-      </c>
-      <c r="J22" s="11" t="n">
-        <v>294.62</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>Esmaltes</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>Suvinil Esmalte Cor &amp; Proteção Base Água Acetinado</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Esmalte Base Água</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>Acetinado</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>3.6L</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>até 60 m²/demão</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>Interno e Externo (metal e madeira)</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>Leroy Merlin</t>
-        </is>
-      </c>
-      <c r="I23" s="11" t="n">
-        <v>289.9</v>
-      </c>
-      <c r="J23" s="10" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Esmaltes</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>Suvinil Esmalte Cor &amp; Proteção Grafite Fosco</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>Esmalte Anticorrosivo</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>Grafite Fosco</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>3.6L</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>até 50 m²/demão</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>Metal (aplica direto na ferrugem)</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>Arena Tintas</t>
-        </is>
-      </c>
-      <c r="I24" s="11" t="n">
-        <v>308.09</v>
-      </c>
-      <c r="J24" s="10" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Especiais</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>Suvinil Epóxi</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>Tinta Epóxi</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Brilhante</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>3.6L</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>até 45 m²/demão</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>Garagens, áreas industriais, cozinhas</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>Arena Tintas</t>
-        </is>
-      </c>
-      <c r="I25" s="11" t="n">
-        <v>327.97</v>
-      </c>
-      <c r="J25" s="10" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>Especiais</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>Suvinil Epóxi</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>Tinta Epóxi</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>Brilhante</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>3.6L</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>até 45 m²/demão</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>Garagens, áreas industriais, cozinhas</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>Leroy Merlin</t>
-        </is>
-      </c>
-      <c r="I26" s="11" t="n">
-        <v>349.9</v>
-      </c>
-      <c r="J26" s="10" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Econômica</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>Suvinil Látex Maxx</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>Tinta Látex Econômica</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>Fosco</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>18L</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>até 280 m²/demão</t>
-        </is>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>Interno</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>Bela Tintas</t>
-        </is>
-      </c>
-      <c r="I27" s="13" t="n">
-        <v>189.9</v>
-      </c>
-      <c r="J27" s="12" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Econômica</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>Suvinil Látex Maxx</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>Tinta Látex Econômica</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>Fosco</t>
-        </is>
-      </c>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>18L</t>
-        </is>
-      </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>até 280 m²/demão</t>
-        </is>
-      </c>
-      <c r="G28" s="12" t="inlineStr">
-        <is>
-          <t>Interno</t>
-        </is>
-      </c>
-      <c r="H28" s="12" t="inlineStr">
-        <is>
-          <t>Mercado Livre</t>
-        </is>
-      </c>
-      <c r="I28" s="13" t="n">
-        <v>169.9</v>
-      </c>
-      <c r="J28" s="12" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Econômica</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>Suvinil Látex Maxx</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>Tinta Látex Econômica</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>Fosco</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>3.6L</t>
-        </is>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>até 56 m²/demão</t>
-        </is>
-      </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>Interno</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>Bela Tintas</t>
-        </is>
-      </c>
-      <c r="I29" s="13" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="J29" s="12" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Pisos</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Suvinil Piso Acrílica</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Tinta Acrílica para Pisos</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Fosco</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>18L</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>até 250 m²/demão</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Pisos de concreto, cimento, cerâmicos</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Leroy Merlin</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>339.9</v>
-      </c>
-      <c r="J30" s="4" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Pisos</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Suvinil Piso Acrílica</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Tinta Acrílica para Pisos</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Fosco</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>18L</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>até 250 m²/demão</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Pisos de concreto, cimento, cerâmicos</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Obramax</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>329.9</v>
-      </c>
-      <c r="J31" s="4" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Suvinil Rende &amp; Cobre Muito Fosco (Obramax 20L)</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Tinta Acrílica Standard</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Fosco</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>20L</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>até 189 m² acabado</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>Interno e Externo</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>Obramax</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>329.9</v>
-      </c>
-      <c r="J32" s="4" t="n"/>
+      <c r="J32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -2138,7 +2149,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Suvinil Toque Fosco Completo (Obramax 20L)</t>
+          <t>Suvinil Toque Fosco Completo</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -2177,145 +2188,933 @@
       <c r="J33" s="6" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Select</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Select</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Alto Padrão</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Fosco Aveludado</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>até 350 m²/demão</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Mercado Livre</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="n">
+        <v>759.73</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>799.72</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Select</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Select</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Alto Padrão</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Fosco Aveludado</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>até 350 m²/demão</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Mercado Livre (2)</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="n">
+        <v>414.76</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>524.9400000000001</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Select</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Select</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Alto Padrão</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Fosco Aveludado</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>até 350 m²/demão</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Arena Tintas</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="n">
+        <v>689</v>
+      </c>
+      <c r="J36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Esmaltes</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Suvinil Esmalte Cor &amp; Proteção Base Água Acetinado</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Esmalte Base Água</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Acetinado</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>até 60 m²/demão</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>Interno e Externo (metal e madeira)</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>Arena Tintas</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="n">
+        <v>265.16</v>
+      </c>
+      <c r="J37" s="11" t="n">
+        <v>294.62</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Esmaltes</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Suvinil Esmalte Cor &amp; Proteção Base Água Acetinado</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Esmalte Base Água</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>Acetinado</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>até 60 m²/demão</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>Interno e Externo (metal e madeira)</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>Leroy Merlin</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="n">
+        <v>289.9</v>
+      </c>
+      <c r="J38" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>Esmaltes</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Suvinil Esmalte Cor &amp; Proteção Grafite Fosco</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Esmalte Anticorrosivo</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Grafite Fosco</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>até 50 m²/demão</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>Metal (aplica direto na ferrugem)</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>Arena Tintas</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="n">
+        <v>308.09</v>
+      </c>
+      <c r="J39" s="10" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Especiais</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Suvinil Epóxi</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Tinta Epóxi</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Brilhante</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>até 45 m²/demão</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>Garagens, áreas industriais, cozinhas</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>Arena Tintas</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="n">
+        <v>327.97</v>
+      </c>
+      <c r="J40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>Especiais</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Suvinil Epóxi</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Tinta Epóxi</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Brilhante</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>até 45 m²/demão</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>Garagens, áreas industriais, cozinhas</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>Leroy Merlin</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="n">
+        <v>349.9</v>
+      </c>
+      <c r="J41" s="10" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>Econômica</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>Suvinil Glasu Econômica (Obramax 20L)</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>Suvinil Glasu Econômica</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>Tinta Acrílica Econômica</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>Fosco</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>até 20 m² acabado</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+      <c r="I42" s="13" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="J42" s="12" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Econômica</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Suvinil Glasu Econômica</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Econômica</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>20L</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F43" s="12" t="inlineStr">
         <is>
           <t>até 200 m²/demão</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>Interno</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr">
+      <c r="H43" s="12" t="inlineStr">
         <is>
           <t>Obramax</t>
         </is>
       </c>
-      <c r="I34" s="13" t="n">
+      <c r="I43" s="13" t="n">
         <v>199.9</v>
       </c>
-      <c r="J34" s="12" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="J43" s="12" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>Econômica</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>Suvinil Látex Maxx</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>Tinta Látex Econômica</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>até 56 m²/demão</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>Bela Tintas</t>
+        </is>
+      </c>
+      <c r="I44" s="13" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="J44" s="12" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Econômica</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>Suvinil Látex Maxx</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>Tinta Látex Econômica</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>até 280 m²/demão</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>Bela Tintas</t>
+        </is>
+      </c>
+      <c r="I45" s="13" t="n">
+        <v>189.9</v>
+      </c>
+      <c r="J45" s="12" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>Econômica</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>Suvinil Látex Maxx</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>Tinta Látex Econômica</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>até 280 m²/demão</t>
+        </is>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>Mercado Livre</t>
+        </is>
+      </c>
+      <c r="I46" s="13" t="n">
+        <v>169.9</v>
+      </c>
+      <c r="J46" s="12" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Econômica</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>Suvinil Gesso &amp; Drywall</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Econômica para Gesso</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>até 24 m² acabado</t>
+        </is>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>Interno (gesso e drywall)</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+      <c r="I47" s="13" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="J47" s="12" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Econômica</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>Suvinil Gesso &amp; Drywall</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica Econômica para Gesso</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>até 180 m²/demão</t>
+        </is>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>Interno (gesso e drywall)</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+      <c r="I48" s="13" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="J48" s="12" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Pisos</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Suvinil Piso Acrílica</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica para Pisos</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>até 250 m²/demão</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>Pisos de concreto, cimento, cerâmicos</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Leroy Merlin</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="J49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Pisos</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Suvinil Piso Acrílica</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Tinta Acrílica para Pisos</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Fosco</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>até 250 m²/demão</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Pisos de concreto, cimento, cerâmicos</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="J50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>Preparação</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>Suvinil Fundo Preparador de Parede</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>Fundo Preparador</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>Transparente</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>até 55 m²/demão</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>Interno e Externo (preparação de superfície)</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="J51" s="14" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Suvinil Inova Fosco Sempre Limpo</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>Tinta Acrílica Premium Anti-Mancha</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>Fosco</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <t>até 350 m²/demão</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G52" s="6" t="inlineStr">
         <is>
           <t>Interno e Externo (lavável)</t>
         </is>
       </c>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="H52" s="6" t="inlineStr">
         <is>
           <t>Arena Tintas</t>
         </is>
       </c>
-      <c r="I35" s="7" t="n">
+      <c r="I52" s="7" t="n">
         <v>499</v>
       </c>
-      <c r="J35" s="6" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="J52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>Suvinil Inova Fosco Sempre Limpo</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>Tinta Acrílica Premium Anti-Mancha</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>Fosco</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <t>até 350 m²/demão</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G53" s="6" t="inlineStr">
         <is>
           <t>Interno e Externo (lavável)</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>Leroy Merlin</t>
         </is>
       </c>
-      <c r="I36" s="7" t="n">
+      <c r="I53" s="7" t="n">
         <v>529.9</v>
       </c>
-      <c r="J36" s="6" t="n"/>
+      <c r="J53" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J36"/>
+  <autoFilter ref="A4:J53"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -2330,7 +3129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2387,435 +3186,638 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Suvinil Rende &amp; Cobre Muito Fosco</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>0.9L</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F4" s="18" t="n">
+        <v>0.1303116147308782</v>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>Arena Tintas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Suvinil Rende &amp; Cobre Muito Fosco</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>128</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>101.74</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>0.602002503128911</v>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Suvinil Rende &amp; Cobre Muito Fosco</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C6" s="17" t="n">
         <v>207.28</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D6" s="17" t="n">
         <v>339.07</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E6" s="17" t="n">
         <v>290.03</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F6" s="18" t="n">
         <v>0.6358066383635661</v>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>Mercado Livre (2)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Suvinil Rende &amp; Cobre Muito Fosco</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>391.69</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>360.795</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>0.1872991815701729</v>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Suvinil Tetos Acrílica Fosca</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>3.6L</t>
         </is>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C8" s="17" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="D8" s="17" t="n">
         <v>79.90000000000001</v>
       </c>
-      <c r="D5" s="15" t="n">
-        <v>95</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>88.26666666666667</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>0.1889862327909886</v>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="E8" s="17" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>0.1430615164520744</v>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>Obramax</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>Suvinil Fosco Completo</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>0.9L</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="D9" s="20" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>Hipertintas</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="D10" s="20" t="n">
+        <v>185.9</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>130.12</v>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>0.8608608608608608</v>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C11" s="20" t="n">
         <v>358.8</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D11" s="20" t="n">
         <v>419.9</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E11" s="20" t="n">
         <v>391.9</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F11" s="21" t="n">
         <v>0.1702898550724637</v>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>Mercado Livre</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>Suvinil Fosco Completo</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="n">
+        <v>449.9</v>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>449.9</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>449.9</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Select</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="n">
+        <v>414.76</v>
+      </c>
+      <c r="D13" s="23" t="n">
+        <v>759.73</v>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>621.1633333333333</v>
+      </c>
+      <c r="F13" s="24" t="n">
+        <v>0.8317340148519626</v>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>Mercado Livre (2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>Suvinil Esmalte Cor &amp; Proteção Base Água Acetinado</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>3.6L</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n">
-        <v>109.9</v>
-      </c>
-      <c r="D7" s="18" t="n">
-        <v>115</v>
-      </c>
-      <c r="E7" s="18" t="n">
-        <v>112.45</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>0.04640582347588711</v>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>Telhanorte</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>Suvinil Toque Fosco Select</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="C14" s="26" t="n">
+        <v>265.16</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>289.9</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>277.53</v>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>0.09330215718811265</v>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
+        <is>
+          <t>Arena Tintas</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>Suvinil Esmalte Cor &amp; Proteção Grafite Fosco</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="n">
+        <v>308.09</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>308.09</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>308.09</v>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="25" t="inlineStr">
+        <is>
+          <t>Arena Tintas</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>Suvinil Epóxi</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="n">
+        <v>327.97</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>349.9</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>338.935</v>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>0.06686587187852532</v>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
+        <is>
+          <t>Arena Tintas</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>Suvinil Glasu Econômica</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="D17" s="29" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="E17" s="29" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="28" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>Suvinil Glasu Econômica</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="D18" s="29" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="E18" s="29" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="28" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>Suvinil Látex Maxx</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="D19" s="29" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="E19" s="29" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="28" t="inlineStr">
+        <is>
+          <t>Bela Tintas</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>Suvinil Látex Maxx</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="C8" s="21" t="n">
-        <v>414.76</v>
-      </c>
-      <c r="D8" s="21" t="n">
-        <v>759.73</v>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>621.1633333333333</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>0.8317340148519626</v>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
-        <is>
-          <t>Mercado Livre (2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="23" t="inlineStr">
-        <is>
-          <t>Suvinil Esmalte Cor &amp; Proteção Base Água Acetinado</t>
-        </is>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="C20" s="29" t="n">
+        <v>169.9</v>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>189.9</v>
+      </c>
+      <c r="E20" s="29" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>0.1177163037080636</v>
+      </c>
+      <c r="G20" s="28" t="inlineStr">
+        <is>
+          <t>Mercado Livre</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>Suvinil Gesso &amp; Drywall</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>3.6L</t>
         </is>
       </c>
-      <c r="C9" s="24" t="n">
-        <v>265.16</v>
-      </c>
-      <c r="D9" s="24" t="n">
-        <v>289.9</v>
-      </c>
-      <c r="E9" s="24" t="n">
-        <v>277.53</v>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>0.09330215718811265</v>
-      </c>
-      <c r="G9" s="23" t="inlineStr">
-        <is>
-          <t>Arena Tintas</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>Suvinil Esmalte Cor &amp; Proteção Grafite Fosco</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="C21" s="29" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="D21" s="29" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="E21" s="29" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="F21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="28" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>Suvinil Gesso &amp; Drywall</t>
+        </is>
+      </c>
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="D22" s="29" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="E22" s="29" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="F22" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="28" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Suvinil Piso Acrílica</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>334.9</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>0.03031221582297666</v>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>Suvinil Fundo Preparador de Parede</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>3.6L</t>
         </is>
       </c>
-      <c r="C10" s="24" t="n">
-        <v>308.09</v>
-      </c>
-      <c r="D10" s="24" t="n">
-        <v>308.09</v>
-      </c>
-      <c r="E10" s="24" t="n">
-        <v>308.09</v>
-      </c>
-      <c r="F10" s="25" t="n">
+      <c r="C24" s="32" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="D24" s="32" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="E24" s="32" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="F24" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>Arena Tintas</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>Suvinil Epóxi</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>3.6L</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="n">
-        <v>327.97</v>
-      </c>
-      <c r="D11" s="24" t="n">
-        <v>349.9</v>
-      </c>
-      <c r="E11" s="24" t="n">
-        <v>338.935</v>
-      </c>
-      <c r="F11" s="25" t="n">
-        <v>0.06686587187852532</v>
-      </c>
-      <c r="G11" s="23" t="inlineStr">
-        <is>
-          <t>Arena Tintas</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>Suvinil Látex Maxx</t>
-        </is>
-      </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="G24" s="31" t="inlineStr">
+        <is>
+          <t>Obramax</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>Suvinil Inova Fosco Sempre Limpo</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="C12" s="27" t="n">
-        <v>169.9</v>
-      </c>
-      <c r="D12" s="27" t="n">
-        <v>189.9</v>
-      </c>
-      <c r="E12" s="27" t="n">
-        <v>179.9</v>
-      </c>
-      <c r="F12" s="28" t="n">
-        <v>0.1177163037080636</v>
-      </c>
-      <c r="G12" s="26" t="inlineStr">
-        <is>
-          <t>Mercado Livre</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="26" t="inlineStr">
-        <is>
-          <t>Suvinil Látex Maxx</t>
-        </is>
-      </c>
-      <c r="B13" s="26" t="inlineStr">
-        <is>
-          <t>3.6L</t>
-        </is>
-      </c>
-      <c r="C13" s="27" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="D13" s="27" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="E13" s="27" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="F13" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="26" t="inlineStr">
-        <is>
-          <t>Bela Tintas</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>Suvinil Piso Acrílica</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>18L</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="n">
-        <v>329.9</v>
-      </c>
-      <c r="D14" s="15" t="n">
-        <v>339.9</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>334.9</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>0.03031221582297666</v>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>Obramax</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Suvinil Rende &amp; Cobre Muito Fosco (Obramax 20L)</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>20L</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="n">
-        <v>329.9</v>
-      </c>
-      <c r="D15" s="15" t="n">
-        <v>329.9</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>329.9</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>Obramax</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>Suvinil Toque Fosco Completo (Obramax 20L)</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>20L</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="n">
-        <v>449.9</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>449.9</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>449.9</v>
-      </c>
-      <c r="F16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>Obramax</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="26" t="inlineStr">
-        <is>
-          <t>Suvinil Glasu Econômica (Obramax 20L)</t>
-        </is>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>20L</t>
-        </is>
-      </c>
-      <c r="C17" s="27" t="n">
-        <v>199.9</v>
-      </c>
-      <c r="D17" s="27" t="n">
-        <v>199.9</v>
-      </c>
-      <c r="E17" s="27" t="n">
-        <v>199.9</v>
-      </c>
-      <c r="F17" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="26" t="inlineStr">
-        <is>
-          <t>Obramax</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>Suvinil Inova Fosco Sempre Limpo</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>18L</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="n">
+      <c r="C25" s="20" t="n">
         <v>499</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D25" s="20" t="n">
         <v>529.9</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E25" s="20" t="n">
         <v>514.45</v>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F25" s="21" t="n">
         <v>0.06192384769539074</v>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="G25" s="19" t="inlineStr">
         <is>
           <t>Arena Tintas</t>
         </is>
@@ -2836,7 +3838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2894,419 +3896,608 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Suvinil Rende &amp; Cobre Muito Fosco</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>0.9L</t>
+        </is>
+      </c>
+      <c r="C5" s="35" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="D5" s="35">
+        <f>C5*0.75</f>
+        <v/>
+      </c>
+      <c r="E5" s="35">
+        <f>C5*0.60</f>
+        <v/>
+      </c>
+      <c r="F5" s="36">
+        <f>(D5-E5)/D5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>Suvinil Rende &amp; Cobre Muito Fosco</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="n">
+        <v>101.74</v>
+      </c>
+      <c r="D6" s="35">
+        <f>C6*0.75</f>
+        <v/>
+      </c>
+      <c r="E6" s="35">
+        <f>C6*0.60</f>
+        <v/>
+      </c>
+      <c r="F6" s="36">
+        <f>(D6-E6)/D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>Suvinil Rende &amp; Cobre Muito Fosco</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="C5" s="30" t="n">
+      <c r="C7" s="35" t="n">
         <v>290.03</v>
       </c>
-      <c r="D5" s="30">
-        <f>C5*0.75</f>
-        <v/>
-      </c>
-      <c r="E5" s="30">
-        <f>C5*0.60</f>
-        <v/>
-      </c>
-      <c r="F5" s="31">
-        <f>(D5-E5)/D5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="D7" s="35">
+        <f>C7*0.75</f>
+        <v/>
+      </c>
+      <c r="E7" s="35">
+        <f>C7*0.60</f>
+        <v/>
+      </c>
+      <c r="F7" s="36">
+        <f>(D7-E7)/D7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Suvinil Rende &amp; Cobre Muito Fosco</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="n">
+        <v>360.795</v>
+      </c>
+      <c r="D8" s="35">
+        <f>C8*0.75</f>
+        <v/>
+      </c>
+      <c r="E8" s="35">
+        <f>C8*0.60</f>
+        <v/>
+      </c>
+      <c r="F8" s="36">
+        <f>(D8-E8)/D8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>Suvinil Tetos Acrílica Fosca</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>3.6L</t>
         </is>
       </c>
-      <c r="C6" s="30" t="n">
-        <v>88.26666666666667</v>
-      </c>
-      <c r="D6" s="30">
-        <f>C6*0.75</f>
-        <v/>
-      </c>
-      <c r="E6" s="30">
-        <f>C6*0.60</f>
-        <v/>
-      </c>
-      <c r="F6" s="31">
-        <f>(D6-E6)/D6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="32" t="inlineStr">
-        <is>
-          <t>Suvinil Fosco Completo</t>
-        </is>
-      </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="C9" s="35" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="D9" s="35">
+        <f>C9*0.75</f>
+        <v/>
+      </c>
+      <c r="E9" s="35">
+        <f>C9*0.60</f>
+        <v/>
+      </c>
+      <c r="F9" s="36">
+        <f>(D9-E9)/D9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo</t>
+        </is>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>0.9L</t>
+        </is>
+      </c>
+      <c r="C10" s="38" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="D10" s="38">
+        <f>C10*0.75</f>
+        <v/>
+      </c>
+      <c r="E10" s="38">
+        <f>C10*0.60</f>
+        <v/>
+      </c>
+      <c r="F10" s="39">
+        <f>(D10-E10)/D10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="37" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo</t>
+        </is>
+      </c>
+      <c r="B11" s="37" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="C11" s="38" t="n">
+        <v>130.12</v>
+      </c>
+      <c r="D11" s="38">
+        <f>C11*0.75</f>
+        <v/>
+      </c>
+      <c r="E11" s="38">
+        <f>C11*0.60</f>
+        <v/>
+      </c>
+      <c r="F11" s="39">
+        <f>(D11-E11)/D11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="37" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="C7" s="33" t="n">
+      <c r="C12" s="38" t="n">
         <v>391.9</v>
       </c>
-      <c r="D7" s="33">
-        <f>C7*0.75</f>
-        <v/>
-      </c>
-      <c r="E7" s="33">
-        <f>C7*0.60</f>
-        <v/>
-      </c>
-      <c r="F7" s="34">
-        <f>(D7-E7)/D7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="32" t="inlineStr">
-        <is>
-          <t>Suvinil Fosco Completo</t>
-        </is>
-      </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="D12" s="38">
+        <f>C12*0.75</f>
+        <v/>
+      </c>
+      <c r="E12" s="38">
+        <f>C12*0.60</f>
+        <v/>
+      </c>
+      <c r="F12" s="39">
+        <f>(D12-E12)/D12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="37" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Completo</t>
+        </is>
+      </c>
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="C13" s="38" t="n">
+        <v>449.9</v>
+      </c>
+      <c r="D13" s="38">
+        <f>C13*0.75</f>
+        <v/>
+      </c>
+      <c r="E13" s="38">
+        <f>C13*0.60</f>
+        <v/>
+      </c>
+      <c r="F13" s="39">
+        <f>(D13-E13)/D13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t>Suvinil Toque Fosco Select</t>
+        </is>
+      </c>
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="C14" s="41" t="n">
+        <v>621.1633333333333</v>
+      </c>
+      <c r="D14" s="41">
+        <f>C14*0.75</f>
+        <v/>
+      </c>
+      <c r="E14" s="41">
+        <f>C14*0.60</f>
+        <v/>
+      </c>
+      <c r="F14" s="42">
+        <f>(D14-E14)/D14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Suvinil Esmalte Cor &amp; Proteção Base Água Acetinado</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
         <is>
           <t>3.6L</t>
         </is>
       </c>
-      <c r="C8" s="33" t="n">
-        <v>112.45</v>
-      </c>
-      <c r="D8" s="33">
-        <f>C8*0.75</f>
-        <v/>
-      </c>
-      <c r="E8" s="33">
-        <f>C8*0.60</f>
-        <v/>
-      </c>
-      <c r="F8" s="34">
-        <f>(D8-E8)/D8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="35" t="inlineStr">
-        <is>
-          <t>Suvinil Toque Fosco Select</t>
-        </is>
-      </c>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="C15" s="44" t="n">
+        <v>277.53</v>
+      </c>
+      <c r="D15" s="44">
+        <f>C15*0.75</f>
+        <v/>
+      </c>
+      <c r="E15" s="44">
+        <f>C15*0.60</f>
+        <v/>
+      </c>
+      <c r="F15" s="45">
+        <f>(D15-E15)/D15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>Suvinil Esmalte Cor &amp; Proteção Grafite Fosco</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="C16" s="44" t="n">
+        <v>308.09</v>
+      </c>
+      <c r="D16" s="44">
+        <f>C16*0.75</f>
+        <v/>
+      </c>
+      <c r="E16" s="44">
+        <f>C16*0.60</f>
+        <v/>
+      </c>
+      <c r="F16" s="45">
+        <f>(D16-E16)/D16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>Suvinil Epóxi</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="C17" s="44" t="n">
+        <v>338.935</v>
+      </c>
+      <c r="D17" s="44">
+        <f>C17*0.75</f>
+        <v/>
+      </c>
+      <c r="E17" s="44">
+        <f>C17*0.60</f>
+        <v/>
+      </c>
+      <c r="F17" s="45">
+        <f>(D17-E17)/D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="46" t="inlineStr">
+        <is>
+          <t>Suvinil Glasu Econômica</t>
+        </is>
+      </c>
+      <c r="B18" s="46" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="C18" s="47" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="D18" s="47">
+        <f>C18*0.75</f>
+        <v/>
+      </c>
+      <c r="E18" s="47">
+        <f>C18*0.60</f>
+        <v/>
+      </c>
+      <c r="F18" s="48">
+        <f>(D18-E18)/D18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="46" t="inlineStr">
+        <is>
+          <t>Suvinil Glasu Econômica</t>
+        </is>
+      </c>
+      <c r="B19" s="46" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="C19" s="47" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="D19" s="47">
+        <f>C19*0.75</f>
+        <v/>
+      </c>
+      <c r="E19" s="47">
+        <f>C19*0.60</f>
+        <v/>
+      </c>
+      <c r="F19" s="48">
+        <f>(D19-E19)/D19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="46" t="inlineStr">
+        <is>
+          <t>Suvinil Látex Maxx</t>
+        </is>
+      </c>
+      <c r="B20" s="46" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+      <c r="C20" s="47" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="D20" s="47">
+        <f>C20*0.75</f>
+        <v/>
+      </c>
+      <c r="E20" s="47">
+        <f>C20*0.60</f>
+        <v/>
+      </c>
+      <c r="F20" s="48">
+        <f>(D20-E20)/D20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="46" t="inlineStr">
+        <is>
+          <t>Suvinil Látex Maxx</t>
+        </is>
+      </c>
+      <c r="B21" s="46" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="C9" s="36" t="n">
-        <v>621.1633333333333</v>
-      </c>
-      <c r="D9" s="36">
-        <f>C9*0.75</f>
-        <v/>
-      </c>
-      <c r="E9" s="36">
-        <f>C9*0.60</f>
-        <v/>
-      </c>
-      <c r="F9" s="37">
-        <f>(D9-E9)/D9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="38" t="inlineStr">
-        <is>
-          <t>Suvinil Esmalte Cor &amp; Proteção Base Água Acetinado</t>
-        </is>
-      </c>
-      <c r="B10" s="38" t="inlineStr">
+      <c r="C21" s="47" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="D21" s="47">
+        <f>C21*0.75</f>
+        <v/>
+      </c>
+      <c r="E21" s="47">
+        <f>C21*0.60</f>
+        <v/>
+      </c>
+      <c r="F21" s="48">
+        <f>(D21-E21)/D21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="46" t="inlineStr">
+        <is>
+          <t>Suvinil Gesso &amp; Drywall</t>
+        </is>
+      </c>
+      <c r="B22" s="46" t="inlineStr">
         <is>
           <t>3.6L</t>
         </is>
       </c>
-      <c r="C10" s="39" t="n">
-        <v>277.53</v>
-      </c>
-      <c r="D10" s="39">
-        <f>C10*0.75</f>
-        <v/>
-      </c>
-      <c r="E10" s="39">
-        <f>C10*0.60</f>
-        <v/>
-      </c>
-      <c r="F10" s="40">
-        <f>(D10-E10)/D10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="38" t="inlineStr">
-        <is>
-          <t>Suvinil Esmalte Cor &amp; Proteção Grafite Fosco</t>
-        </is>
-      </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="C22" s="47" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="D22" s="47">
+        <f>C22*0.75</f>
+        <v/>
+      </c>
+      <c r="E22" s="47">
+        <f>C22*0.60</f>
+        <v/>
+      </c>
+      <c r="F22" s="48">
+        <f>(D22-E22)/D22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="46" t="inlineStr">
+        <is>
+          <t>Suvinil Gesso &amp; Drywall</t>
+        </is>
+      </c>
+      <c r="B23" s="46" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="C23" s="47" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="D23" s="47">
+        <f>C23*0.75</f>
+        <v/>
+      </c>
+      <c r="E23" s="47">
+        <f>C23*0.60</f>
+        <v/>
+      </c>
+      <c r="F23" s="48">
+        <f>(D23-E23)/D23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="34" t="inlineStr">
+        <is>
+          <t>Suvinil Piso Acrílica</t>
+        </is>
+      </c>
+      <c r="B24" s="34" t="inlineStr">
+        <is>
+          <t>18L</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="n">
+        <v>334.9</v>
+      </c>
+      <c r="D24" s="35">
+        <f>C24*0.75</f>
+        <v/>
+      </c>
+      <c r="E24" s="35">
+        <f>C24*0.60</f>
+        <v/>
+      </c>
+      <c r="F24" s="36">
+        <f>(D24-E24)/D24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="49" t="inlineStr">
+        <is>
+          <t>Suvinil Fundo Preparador de Parede</t>
+        </is>
+      </c>
+      <c r="B25" s="49" t="inlineStr">
         <is>
           <t>3.6L</t>
         </is>
       </c>
-      <c r="C11" s="39" t="n">
-        <v>308.09</v>
-      </c>
-      <c r="D11" s="39">
-        <f>C11*0.75</f>
-        <v/>
-      </c>
-      <c r="E11" s="39">
-        <f>C11*0.60</f>
-        <v/>
-      </c>
-      <c r="F11" s="40">
-        <f>(D11-E11)/D11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="38" t="inlineStr">
-        <is>
-          <t>Suvinil Epóxi</t>
-        </is>
-      </c>
-      <c r="B12" s="38" t="inlineStr">
-        <is>
-          <t>3.6L</t>
-        </is>
-      </c>
-      <c r="C12" s="39" t="n">
-        <v>338.935</v>
-      </c>
-      <c r="D12" s="39">
-        <f>C12*0.75</f>
-        <v/>
-      </c>
-      <c r="E12" s="39">
-        <f>C12*0.60</f>
-        <v/>
-      </c>
-      <c r="F12" s="40">
-        <f>(D12-E12)/D12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="41" t="inlineStr">
-        <is>
-          <t>Suvinil Látex Maxx</t>
-        </is>
-      </c>
-      <c r="B13" s="41" t="inlineStr">
+      <c r="C25" s="50" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="D25" s="50">
+        <f>C25*0.75</f>
+        <v/>
+      </c>
+      <c r="E25" s="50">
+        <f>C25*0.60</f>
+        <v/>
+      </c>
+      <c r="F25" s="51">
+        <f>(D25-E25)/D25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="37" t="inlineStr">
+        <is>
+          <t>Suvinil Inova Fosco Sempre Limpo</t>
+        </is>
+      </c>
+      <c r="B26" s="37" t="inlineStr">
         <is>
           <t>18L</t>
         </is>
       </c>
-      <c r="C13" s="42" t="n">
-        <v>179.9</v>
-      </c>
-      <c r="D13" s="42">
-        <f>C13*0.75</f>
-        <v/>
-      </c>
-      <c r="E13" s="42">
-        <f>C13*0.60</f>
-        <v/>
-      </c>
-      <c r="F13" s="43">
-        <f>(D13-E13)/D13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="41" t="inlineStr">
-        <is>
-          <t>Suvinil Látex Maxx</t>
-        </is>
-      </c>
-      <c r="B14" s="41" t="inlineStr">
-        <is>
-          <t>3.6L</t>
-        </is>
-      </c>
-      <c r="C14" s="42" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="D14" s="42">
-        <f>C14*0.75</f>
-        <v/>
-      </c>
-      <c r="E14" s="42">
-        <f>C14*0.60</f>
-        <v/>
-      </c>
-      <c r="F14" s="43">
-        <f>(D14-E14)/D14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="29" t="inlineStr">
-        <is>
-          <t>Suvinil Piso Acrílica</t>
-        </is>
-      </c>
-      <c r="B15" s="29" t="inlineStr">
-        <is>
-          <t>18L</t>
-        </is>
-      </c>
-      <c r="C15" s="30" t="n">
-        <v>334.9</v>
-      </c>
-      <c r="D15" s="30">
-        <f>C15*0.75</f>
-        <v/>
-      </c>
-      <c r="E15" s="30">
-        <f>C15*0.60</f>
-        <v/>
-      </c>
-      <c r="F15" s="31">
-        <f>(D15-E15)/D15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="29" t="inlineStr">
-        <is>
-          <t>Suvinil Rende &amp; Cobre Muito Fosco (Obramax 20L)</t>
-        </is>
-      </c>
-      <c r="B16" s="29" t="inlineStr">
-        <is>
-          <t>20L</t>
-        </is>
-      </c>
-      <c r="C16" s="30" t="n">
-        <v>329.9</v>
-      </c>
-      <c r="D16" s="30">
-        <f>C16*0.75</f>
-        <v/>
-      </c>
-      <c r="E16" s="30">
-        <f>C16*0.60</f>
-        <v/>
-      </c>
-      <c r="F16" s="31">
-        <f>(D16-E16)/D16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="32" t="inlineStr">
-        <is>
-          <t>Suvinil Toque Fosco Completo (Obramax 20L)</t>
-        </is>
-      </c>
-      <c r="B17" s="32" t="inlineStr">
-        <is>
-          <t>20L</t>
-        </is>
-      </c>
-      <c r="C17" s="33" t="n">
-        <v>449.9</v>
-      </c>
-      <c r="D17" s="33">
-        <f>C17*0.75</f>
-        <v/>
-      </c>
-      <c r="E17" s="33">
-        <f>C17*0.60</f>
-        <v/>
-      </c>
-      <c r="F17" s="34">
-        <f>(D17-E17)/D17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="41" t="inlineStr">
-        <is>
-          <t>Suvinil Glasu Econômica (Obramax 20L)</t>
-        </is>
-      </c>
-      <c r="B18" s="41" t="inlineStr">
-        <is>
-          <t>20L</t>
-        </is>
-      </c>
-      <c r="C18" s="42" t="n">
-        <v>199.9</v>
-      </c>
-      <c r="D18" s="42">
-        <f>C18*0.75</f>
-        <v/>
-      </c>
-      <c r="E18" s="42">
-        <f>C18*0.60</f>
-        <v/>
-      </c>
-      <c r="F18" s="43">
-        <f>(D18-E18)/D18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="32" t="inlineStr">
-        <is>
-          <t>Suvinil Inova Fosco Sempre Limpo</t>
-        </is>
-      </c>
-      <c r="B19" s="32" t="inlineStr">
-        <is>
-          <t>18L</t>
-        </is>
-      </c>
-      <c r="C19" s="33" t="n">
+      <c r="C26" s="38" t="n">
         <v>514.45</v>
       </c>
-      <c r="D19" s="33">
-        <f>C19*0.75</f>
-        <v/>
-      </c>
-      <c r="E19" s="33">
-        <f>C19*0.60</f>
-        <v/>
-      </c>
-      <c r="F19" s="34">
-        <f>(D19-E19)/D19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="44" t="inlineStr">
+      <c r="D26" s="38">
+        <f>C26*0.75</f>
+        <v/>
+      </c>
+      <c r="E26" s="38">
+        <f>C26*0.60</f>
+        <v/>
+      </c>
+      <c r="F26" s="39">
+        <f>(D26-E26)/D26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="52" t="inlineStr">
         <is>
           <t>AVISO: Os preços estimados de distribuidor e fábrica são aproximações baseadas em margens típicas do setor.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="44" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="52" t="inlineStr">
         <is>
           <t>Margens reais variam conforme volume, negociação e política comercial de cada fabricante.</t>
         </is>
@@ -3336,262 +4527,262 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="53" t="inlineStr">
         <is>
           <t>FONTES DE PREÇOS CONSULTADAS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="46" t="inlineStr">
+      <c r="A3" s="54" t="inlineStr">
         <is>
           <t>Fonte</t>
         </is>
       </c>
-      <c r="B3" s="46" t="inlineStr">
+      <c r="B3" s="54" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="C3" s="46" t="inlineStr">
+      <c r="C3" s="54" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="47" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>Loja Suvinil (Oficial)</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>https://loja.suvinil.com.br/</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>E-commerce oficial</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="47" t="inlineStr">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>Arena Tintas</t>
         </is>
       </c>
-      <c r="B5" s="47" t="inlineStr">
+      <c r="B5" s="49" t="inlineStr">
         <is>
           <t>https://arenatintas.com/suvinil</t>
         </is>
       </c>
-      <c r="C5" s="47" t="inlineStr">
+      <c r="C5" s="49" t="inlineStr">
         <is>
           <t>Varejo online</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="49" t="inlineStr">
         <is>
           <t>Bela Tintas</t>
         </is>
       </c>
-      <c r="B6" s="47" t="inlineStr">
+      <c r="B6" s="49" t="inlineStr">
         <is>
           <t>https://www.belatintas.com.br/suvinil</t>
         </is>
       </c>
-      <c r="C6" s="47" t="inlineStr">
+      <c r="C6" s="49" t="inlineStr">
         <is>
           <t>Varejo online</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>Leroy Merlin</t>
         </is>
       </c>
-      <c r="B7" s="47" t="inlineStr">
+      <c r="B7" s="49" t="inlineStr">
         <is>
           <t>https://www.leroymerlin.com.br/tintas/marca/Suvinil</t>
         </is>
       </c>
-      <c r="C7" s="47" t="inlineStr">
+      <c r="C7" s="49" t="inlineStr">
         <is>
           <t>Home center</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="49" t="inlineStr">
         <is>
           <t>Telhanorte</t>
         </is>
       </c>
-      <c r="B8" s="47" t="inlineStr">
+      <c r="B8" s="49" t="inlineStr">
         <is>
           <t>https://www.telhanorte.com.br/suvinil</t>
         </is>
       </c>
-      <c r="C8" s="47" t="inlineStr">
+      <c r="C8" s="49" t="inlineStr">
         <is>
           <t>Home center</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="47" t="inlineStr">
+      <c r="A9" s="49" t="inlineStr">
         <is>
           <t>Mercado Livre</t>
         </is>
       </c>
-      <c r="B9" s="47" t="inlineStr">
+      <c r="B9" s="49" t="inlineStr">
         <is>
           <t>https://lista.mercadolivre.com.br/tinta-suvinil-18-litros</t>
         </is>
       </c>
-      <c r="C9" s="47" t="inlineStr">
+      <c r="C9" s="49" t="inlineStr">
         <is>
           <t>Marketplace</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="47" t="inlineStr">
+      <c r="A10" s="49" t="inlineStr">
         <is>
           <t>Varejão das Tintas</t>
         </is>
       </c>
-      <c r="B10" s="47" t="inlineStr">
+      <c r="B10" s="49" t="inlineStr">
         <is>
           <t>https://loja.varejaodastintas.com.br/marca/suvinil.html</t>
         </is>
       </c>
-      <c r="C10" s="47" t="inlineStr">
+      <c r="C10" s="49" t="inlineStr">
         <is>
           <t>Varejo online</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="47" t="inlineStr">
+      <c r="A11" s="49" t="inlineStr">
         <is>
           <t>Casa Costa Tintas</t>
         </is>
       </c>
-      <c r="B11" s="47" t="inlineStr">
+      <c r="B11" s="49" t="inlineStr">
         <is>
           <t>https://www.casacostatintas.com.br/</t>
         </is>
       </c>
-      <c r="C11" s="47" t="inlineStr">
+      <c r="C11" s="49" t="inlineStr">
         <is>
           <t>Varejo online</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="47" t="inlineStr">
+      <c r="A12" s="49" t="inlineStr">
         <is>
           <t>Hipertintas</t>
         </is>
       </c>
-      <c r="B12" s="47" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>https://www.hipertintas.com.br/tintas/parede/suvinil/18</t>
         </is>
       </c>
-      <c r="C12" s="47" t="inlineStr">
+      <c r="C12" s="49" t="inlineStr">
         <is>
           <t>Varejo online</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="47" t="inlineStr">
+      <c r="A13" s="49" t="inlineStr">
         <is>
           <t>Buscapé</t>
         </is>
       </c>
-      <c r="B13" s="47" t="inlineStr">
+      <c r="B13" s="49" t="inlineStr">
         <is>
           <t>https://www.buscape.com.br/busca/tinta+suvinil+18+litros</t>
         </is>
       </c>
-      <c r="C13" s="47" t="inlineStr">
+      <c r="C13" s="49" t="inlineStr">
         <is>
           <t>Comparador de preços</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="47" t="inlineStr">
+      <c r="A14" s="49" t="inlineStr">
         <is>
           <t>Obramax</t>
         </is>
       </c>
-      <c r="B14" s="47" t="inlineStr">
+      <c r="B14" s="49" t="inlineStr">
         <is>
           <t>https://www.obramax.com.br/suvinil</t>
         </is>
       </c>
-      <c r="C14" s="47" t="inlineStr">
+      <c r="C14" s="49" t="inlineStr">
         <is>
           <t>Home center atacado/varejo</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="49" t="inlineStr">
         <is>
           <t>Cofema Atacadista</t>
         </is>
       </c>
-      <c r="B15" s="47" t="inlineStr">
+      <c r="B15" s="49" t="inlineStr">
         <is>
           <t>https://www.cofema.com.br/</t>
         </is>
       </c>
-      <c r="C15" s="47" t="inlineStr">
+      <c r="C15" s="49" t="inlineStr">
         <is>
           <t>Atacadista materiais construção</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="47" t="inlineStr">
+      <c r="A16" s="49" t="inlineStr">
         <is>
           <t>Eletroleste</t>
         </is>
       </c>
-      <c r="B16" s="47" t="inlineStr">
+      <c r="B16" s="49" t="inlineStr">
         <is>
           <t>https://www.eletroleste.com.br/</t>
         </is>
       </c>
-      <c r="C16" s="47" t="inlineStr">
+      <c r="C16" s="49" t="inlineStr">
         <is>
           <t>Atacadista materiais construção</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="47" t="inlineStr">
+      <c r="A17" s="49" t="inlineStr">
         <is>
           <t>Ismafer</t>
         </is>
       </c>
-      <c r="B17" s="47" t="inlineStr">
+      <c r="B17" s="49" t="inlineStr">
         <is>
           <t>https://www.ismafer.com.br/</t>
         </is>
       </c>
-      <c r="C17" s="47" t="inlineStr">
+      <c r="C17" s="49" t="inlineStr">
         <is>
           <t>Varejo ferragens e ferramentas</t>
         </is>
